--- a/Datos ESPARTACO/Visualizacion_velocidades/recopliacion_velocidades.xlsx
+++ b/Datos ESPARTACO/Visualizacion_velocidades/recopliacion_velocidades.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e0f5dede0e73560/- Universidad de los andes/2026-2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e0f5dede0e73560/- Universidad de los andes/TESIS/Tesis/Datos ESPARTACO/Visualizacion_velocidades/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{1667F798-5643-45DD-A94B-0D5A47E8D07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
